--- a/artfynd/A 25180-2022 artfynd.xlsx
+++ b/artfynd/A 25180-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680354</v>
+        <v>121680704</v>
       </c>
       <c r="B2" t="n">
-        <v>57376</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräsmossen, Dlr</t>
+          <t>Näverberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569764</v>
+        <v>569849</v>
       </c>
       <c r="R2" t="n">
-        <v>6663810</v>
+        <v>6663864</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680704</v>
+        <v>121680354</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,14 +845,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverberget, Dlr</t>
+          <t>Gräsmossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569849</v>
+        <v>569764</v>
       </c>
       <c r="R3" t="n">
-        <v>6663864</v>
+        <v>6663810</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 25180-2022 artfynd.xlsx
+++ b/artfynd/A 25180-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680704</v>
+        <v>121680354</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>57376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverberget, Dlr</t>
+          <t>Gräsmossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569849</v>
+        <v>569764</v>
       </c>
       <c r="R2" t="n">
-        <v>6663864</v>
+        <v>6663810</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680354</v>
+        <v>121680704</v>
       </c>
       <c r="B3" t="n">
-        <v>57376</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,14 +845,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräsmossen, Dlr</t>
+          <t>Näverberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569764</v>
+        <v>569849</v>
       </c>
       <c r="R3" t="n">
-        <v>6663810</v>
+        <v>6663864</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 25180-2022 artfynd.xlsx
+++ b/artfynd/A 25180-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121680354</v>
       </c>
       <c r="B2" t="n">
-        <v>57376</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>121680704</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 25180-2022 artfynd.xlsx
+++ b/artfynd/A 25180-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680354</v>
+        <v>121680704</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>57385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräsmossen, Dlr</t>
+          <t>Näverberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569764</v>
+        <v>569849</v>
       </c>
       <c r="R2" t="n">
-        <v>6663810</v>
+        <v>6663864</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680704</v>
+        <v>121680354</v>
       </c>
       <c r="B3" t="n">
-        <v>57381</v>
+        <v>57388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,14 +845,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverberget, Dlr</t>
+          <t>Gräsmossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569849</v>
+        <v>569764</v>
       </c>
       <c r="R3" t="n">
-        <v>6663864</v>
+        <v>6663810</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
